--- a/samples/system_ibt_500_ingest.xlsx
+++ b/samples/system_ibt_500_ingest.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,10 +475,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Rule Profile</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>IBT_500_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Sumber</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Buku Kerawanan SJB 2026 Sec 1.5, Gambar 1.5 (PDF p.40-64); jaringan 500 kV sama dengan view Transmisi, stub IBT diturunkan dari baris IBT pada workbook subsistem</t>
         </is>
@@ -9953,12 +9965,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[N-1] [Suralaya Unit #3 - Suralaya 1,2-Cilegon 4] Daya Mampu Pasok IBT Suralaya dan Cilegon tidak sama (IBT #1,2 Suralaya 250 MVA sedangkan IBT #4 Cilegon 500 MVA)</t>
+          <t>[BELUM_DITETAPKAN] [Suralaya Unit #3 - Suralaya 1,2-Cilegon 4] Daya Mampu Pasok IBT Suralaya dan Cilegon tidak sama (IBT #1,2 Suralaya 250 MVA sedangkan IBT #4 Cilegon 500 MVA)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -10163,12 +10175,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[N-1] [Cibatu 3,4 - mandirancan 1,2] IBT 1,2 GITET Mandirancan sudah berbeban &gt;60% (@87%) saat PLTU CEP atau PLTU Indramayu outage</t>
+          <t>[BELUM_DITETAPKAN] [Cibatu 3,4 - mandirancan 1,2] IBT 1,2 GITET Mandirancan sudah berbeban &gt;60% (@87%) saat PLTU CEP atau PLTU Indramayu outage</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -10198,12 +10210,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[N-1] [Cirata 1,2,3] 1.Pembebanan IBT 1, 2 &amp; 3 GITET Cirata sudah di atas 60% (IBT-1,2 @77%, IBT-3 82%) kondisi operasi parallel 3 IBT, looping jauh 3 IBT 500/150 kV GITET Cirata di Penghantar SUTT 150 kV Cirata - Cikumpay - Purwakarta. 2.Besarnya Short Circuit Level (&gt;40 kA) di GI 150 kV Cirata apabila seluruh unit PLTA Cirata, PLTA Saguling, dan minimal 2 unit PLTA Jatiluhur dioperasikan di SS Cirata 1,2,3</t>
+          <t>[BELUM_DITETAPKAN] [Cirata 1,2,3] 1.Pembebanan IBT 1, 2 &amp; 3 GITET Cirata sudah di atas 60% (IBT-1,2 @77%, IBT-3 82%) kondisi operasi parallel 3 IBT, looping jauh 3 IBT 500/150 kV GITET Cirata di Penghantar SUTT 150 kV Cirata - Cikumpay - Purwakarta. 2.Besarnya Short Circuit Level (&gt;40 kA) di GI 150 kV Cirata apabila seluruh unit PLTA Cirata, PLTA Saguling, dan minimal 2 unit PLTA Jatiluhur dioperasikan di SS Cirata 1,2,3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -10303,12 +10315,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[N-1] [Deltamas 1,2] Pembebanan IBT 1 &amp; 2 GITET Deltamasberpote nsi naikdiatas50%</t>
+          <t>[BELUM_DITETAPKAN] [Deltamas 1,2] Pembebanan IBT 1 &amp; 2 GITET Deltamasberpote nsi naikdiatas50%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -10548,12 +10560,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>N-1-1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[N-1] [Tanjung Jati 1,2 -Ungaran 3] IBT-3 Ungaran akan mengalami overload apabila terjadi kontingensi N-1-1 pada IBT Tanjungjati 1,2</t>
+          <t>[N-1-1] [Tanjung Jati 1,2 -Ungaran 3] IBT-3 Ungaran akan mengalami overload apabila terjadi kontingensi N-1-1 pada IBT Tanjungjati 1,2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -10583,12 +10595,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[N-1] [Tanjung Jati 1,2 -Ungaran 3] IBT-3 Ungaran yang memasok Subsistem Tanjung Jati mayoritas konsumen industri (MVAR- nya besar) untuk pasokan wilayah Magelang &amp; Kudus sehingga berpotensi drop tegangan</t>
+          <t>[BELUM_DITETAPKAN] [Tanjung Jati 1,2 -Ungaran 3] IBT-3 Ungaran yang memasok Subsistem Tanjung Jati mayoritas konsumen industri (MVAR- nya besar) untuk pasokan wilayah Magelang &amp; Kudus sehingga berpotensi drop tegangan</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10758,12 +10770,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[N-1] [Pedan 3,4] Pembebanan IBT 1/2/3/4 GITET Pedan &gt;60% jika operasi looping IBT 1,2 dan 3,4 Pedan saat pemeliharaan pada salah satu IBT</t>
+          <t>[BELUM_DITETAPKAN] [Pedan 3,4] Pembebanan IBT 1/2/3/4 GITET Pedan &gt;60% jika operasi looping IBT 1,2 dan 3,4 Pedan saat pemeliharaan pada salah satu IBT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11038,12 +11050,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>N-1-1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>[N-1] [Ngimbang 1,2] Beban IBT Ngimbang akan berbeban lebih 70% apabila terjadi N-1-1 pada PLTU Tanjung awar- awar sehingga tidak memenuhi kriteria N-1 IBT tersebut</t>
+          <t>[N-1-1] [Ngimbang 1,2] Beban IBT Ngimbang akan berbeban lebih 70% apabila terjadi N-1-1 pada PLTU Tanjung awar- awar sehingga tidak memenuhi kriteria N-1 IBT tersebut</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">

--- a/samples/system_ibt_500_ingest.xlsx
+++ b/samples/system_ibt_500_ingest.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LBE</t>
+          <t>LBE7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KIT_LBE</t>
+          <t>KIT_LBE7</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NSRLA</t>
+          <t>NSRLA7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KIT_NSRLA</t>
+          <t>KIT_NSRLA7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SRLYA</t>
+          <t>SRLYA7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KIT_SRLYA</t>
+          <t>KIT_SRLYA7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JAWA910</t>
+          <t>JAWA9107</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KIT_JAWA910</t>
+          <t>KIT_JAWA9107</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PRIDK</t>
+          <t>PRIDK7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KIT_PRIDK</t>
+          <t>KIT_PRIDK7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MTWAR</t>
+          <t>MTWAR7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KIT_MTWAR</t>
+          <t>KIT_MTWAR7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLMYA</t>
+          <t>CLMYA7</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>KIT_CLMYA</t>
+          <t>KIT_CLMYA7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CRATA</t>
+          <t>CRATA7</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KIT_CRATA</t>
+          <t>KIT_CRATA7</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SGLNG</t>
+          <t>SGLNG7</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>KIT_SGLNG</t>
+          <t>KIT_SGLNG7</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ADPLA</t>
+          <t>ADPLA7</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>KIT_ADPLA</t>
+          <t>KIT_ADPLA7</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLCAP</t>
+          <t>CLCAP7</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>KIT_CLCAP</t>
+          <t>KIT_CLCAP7</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BTANG</t>
+          <t>BTANG7</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KIT_BTANG</t>
+          <t>KIT_BTANG7</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NTJTI</t>
+          <t>NTJTI7</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>KIT_NTJTI</t>
+          <t>KIT_NTJTI7</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TJATI</t>
+          <t>TJATI7</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KIT_TJATI</t>
+          <t>KIT_TJATI7</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GRSIK</t>
+          <t>GRSIK7</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>KIT_GRSIK</t>
+          <t>KIT_GRSIK7</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GRATI</t>
+          <t>GRATI7</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KIT_GRATI</t>
+          <t>KIT_GRATI7</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PITON</t>
+          <t>PITON7</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>KIT_PITON</t>
+          <t>KIT_PITON7</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BLRJA</t>
+          <t>BLRJA7</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CLGON</t>
+          <t>CLGON7</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TMBUN</t>
+          <t>TMBUN7</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CWANG</t>
+          <t>CWANG7</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SKTNI</t>
+          <t>SKTNI7</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DLTMS</t>
+          <t>DLTMS7</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CIBNG</t>
+          <t>CIBNG7</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BDSLN</t>
+          <t>BDSLN7</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>KSGHN</t>
+          <t>KSGHN7</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PMLNG</t>
+          <t>PMLNG7</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UNGRN</t>
+          <t>UNGRN7</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>KRIAN</t>
+          <t>KRIAN7</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>KDIRI</t>
+          <t>KDIRI7</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>LNGKG</t>
+          <t>LNGKG7</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>KMBNG</t>
+          <t>KMBNG7</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BKASI</t>
+          <t>BKASI7</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CBATU</t>
+          <t>CBATU7</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>UBRNG</t>
+          <t>UBRNG7</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>IDMYU</t>
+          <t>IDMYU7</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MDCAN</t>
+          <t>MDCAN7</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TSMYA</t>
+          <t>TSMYA7</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BYOLI</t>
+          <t>BYOLI7</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PEDAN</t>
+          <t>PEDAN7</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NBANG</t>
+          <t>NBANG7</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DEPOK</t>
+          <t>DEPOK7</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GNDUL</t>
+          <t>GNDUL7</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DKSBI</t>
+          <t>DKSBI7</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MKRNG</t>
+          <t>MKRNG7</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BLRJA</t>
+          <t>BLRJA7</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LBE</t>
+          <t>LBE7</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SRLYA</t>
+          <t>SRLYA7</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NSRLA</t>
+          <t>NSRLA7</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NSRLA</t>
+          <t>NSRLA7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LBE</t>
+          <t>LBE7</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SRLYA</t>
+          <t>SRLYA7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BLRJA</t>
+          <t>BLRJA7</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SRLYA</t>
+          <t>SRLYA7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CLGON</t>
+          <t>CLGON7</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JAWA910</t>
+          <t>JAWA9107</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CLGON</t>
+          <t>CLGON7</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BLRJA</t>
+          <t>BLRJA7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LNGKG</t>
+          <t>LNGKG7</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LBE</t>
+          <t>LBE7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BLRJA</t>
+          <t>BLRJA7</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CLGON</t>
+          <t>CLGON7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CIBNG</t>
+          <t>CIBNG7</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>GNDUL</t>
+          <t>GNDUL7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>DEPOK</t>
+          <t>DEPOK7</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -4871,12 +4871,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DEPOK</t>
+          <t>DEPOK7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CIBNG</t>
+          <t>CIBNG7</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -4930,12 +4930,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LNGKG</t>
+          <t>LNGKG7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GNDUL</t>
+          <t>GNDUL7</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KMBNG</t>
+          <t>KMBNG7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>GNDUL</t>
+          <t>GNDUL7</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -5048,12 +5048,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>GNDUL</t>
+          <t>GNDUL7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>DKSBI</t>
+          <t>DKSBI7</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>KMBNG</t>
+          <t>KMBNG7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>DKSBI</t>
+          <t>DKSBI7</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DKSBI</t>
+          <t>DKSBI7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MKRNG</t>
+          <t>MKRNG7</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -5225,12 +5225,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MTWAR</t>
+          <t>MTWAR7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CWANG</t>
+          <t>CWANG7</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MTWAR</t>
+          <t>MTWAR7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TMBUN</t>
+          <t>TMBUN7</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TMBUN</t>
+          <t>TMBUN7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BKASI</t>
+          <t>BKASI7</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -5402,12 +5402,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>BKASI</t>
+          <t>BKASI7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MTWAR</t>
+          <t>MTWAR7</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MTWAR</t>
+          <t>MTWAR7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PRIDK</t>
+          <t>PRIDK7</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PRIDK</t>
+          <t>PRIDK7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MKRNG</t>
+          <t>MKRNG7</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CWANG</t>
+          <t>CWANG7</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>GNDUL</t>
+          <t>GNDUL7</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SKTNI</t>
+          <t>SKTNI7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CLMYA</t>
+          <t>CLMYA7</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5697,12 +5697,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SKTNI</t>
+          <t>SKTNI7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CBATU</t>
+          <t>CBATU7</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5756,12 +5756,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DLTMS</t>
+          <t>DLTMS7</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CBATU</t>
+          <t>CBATU7</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CRATA</t>
+          <t>CRATA7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SKTNI</t>
+          <t>SKTNI7</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SGLNG</t>
+          <t>SGLNG7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>BDSLN</t>
+          <t>BDSLN7</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>BDSLN</t>
+          <t>BDSLN7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UBRNG</t>
+          <t>UBRNG7</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MDCAN</t>
+          <t>MDCAN7</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UBRNG</t>
+          <t>UBRNG7</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>MDCAN</t>
+          <t>MDCAN7</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>BDSLN</t>
+          <t>BDSLN7</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CIBNG</t>
+          <t>CIBNG7</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IDMYU</t>
+          <t>IDMYU7</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6169,12 +6169,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>IDMYU</t>
+          <t>IDMYU7</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MDCAN</t>
+          <t>MDCAN7</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>TSMYA</t>
+          <t>TSMYA7</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>BDSLN</t>
+          <t>BDSLN7</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -6287,12 +6287,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>TSMYA</t>
+          <t>TSMYA7</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>DEPOK</t>
+          <t>DEPOK7</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>KSGHN</t>
+          <t>KSGHN7</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>TSMYA</t>
+          <t>TSMYA7</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -6405,12 +6405,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>KSGHN</t>
+          <t>KSGHN7</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ADPLA</t>
+          <t>ADPLA7</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ADPLA</t>
+          <t>ADPLA7</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CLCAP</t>
+          <t>CLCAP7</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>PMLNG</t>
+          <t>PMLNG7</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>BTANG</t>
+          <t>BTANG7</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>PMLNG</t>
+          <t>PMLNG7</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>NTJTI</t>
+          <t>NTJTI7</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NTJTI</t>
+          <t>NTJTI7</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>UNGRN</t>
+          <t>UNGRN7</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>TJATI</t>
+          <t>TJATI7</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>UNGRN</t>
+          <t>UNGRN7</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>KSGHN</t>
+          <t>KSGHN7</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>MDCAN</t>
+          <t>MDCAN7</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KSGHN</t>
+          <t>KSGHN7</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PMLNG</t>
+          <t>PMLNG7</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -6877,12 +6877,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>UNGRN</t>
+          <t>UNGRN7</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>BYOLI</t>
+          <t>BYOLI7</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -6936,12 +6936,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>BYOLI</t>
+          <t>BYOLI7</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PEDAN</t>
+          <t>PEDAN7</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -6995,12 +6995,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>UNGRN</t>
+          <t>UNGRN7</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KRIAN</t>
+          <t>KRIAN7</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -7054,12 +7054,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>UNGRN</t>
+          <t>UNGRN7</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>NBANG</t>
+          <t>NBANG7</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -7113,12 +7113,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>PITON</t>
+          <t>PITON7</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>GRATI</t>
+          <t>GRATI7</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>GRATI</t>
+          <t>GRATI7</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KRIAN</t>
+          <t>KRIAN7</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>PITON</t>
+          <t>PITON7</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KDIRI</t>
+          <t>KDIRI7</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>KDIRI</t>
+          <t>KDIRI7</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>PEDAN</t>
+          <t>PEDAN7</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -7349,12 +7349,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>KRIAN</t>
+          <t>KRIAN7</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>GRSIK</t>
+          <t>GRSIK7</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>KRIAN</t>
+          <t>KRIAN7</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>NBANG</t>
+          <t>NBANG7</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>KIT_LBE</t>
+          <t>KIT_LBE7</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>LBE</t>
+          <t>LBE7</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -7585,12 +7585,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KIT_NSRLA</t>
+          <t>KIT_NSRLA7</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>NSRLA</t>
+          <t>NSRLA7</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>KIT_SRLYA</t>
+          <t>KIT_SRLYA7</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SRLYA</t>
+          <t>SRLYA7</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>KIT_JAWA910</t>
+          <t>KIT_JAWA9107</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>JAWA910</t>
+          <t>JAWA9107</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7762,12 +7762,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KIT_PRIDK</t>
+          <t>KIT_PRIDK7</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PRIDK</t>
+          <t>PRIDK7</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KIT_MTWAR</t>
+          <t>KIT_MTWAR7</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MTWAR</t>
+          <t>MTWAR7</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KIT_CLMYA</t>
+          <t>KIT_CLMYA7</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CLMYA</t>
+          <t>CLMYA7</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>KIT_CRATA</t>
+          <t>KIT_CRATA7</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CRATA</t>
+          <t>CRATA7</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7998,12 +7998,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>KIT_SGLNG</t>
+          <t>KIT_SGLNG7</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>SGLNG</t>
+          <t>SGLNG7</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>KIT_ADPLA</t>
+          <t>KIT_ADPLA7</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ADPLA</t>
+          <t>ADPLA7</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -8116,12 +8116,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>KIT_CLCAP</t>
+          <t>KIT_CLCAP7</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CLCAP</t>
+          <t>CLCAP7</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>KIT_BTANG</t>
+          <t>KIT_BTANG7</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>BTANG</t>
+          <t>BTANG7</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KIT_NTJTI</t>
+          <t>KIT_NTJTI7</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>NTJTI</t>
+          <t>NTJTI7</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>KIT_TJATI</t>
+          <t>KIT_TJATI7</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>TJATI</t>
+          <t>TJATI7</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>KIT_GRSIK</t>
+          <t>KIT_GRSIK7</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>GRSIK</t>
+          <t>GRSIK7</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -8411,12 +8411,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>KIT_GRATI</t>
+          <t>KIT_GRATI7</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>GRATI</t>
+          <t>GRATI7</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -8470,12 +8470,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>KIT_PITON</t>
+          <t>KIT_PITON7</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>PITON</t>
+          <t>PITON7</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8584,17 +8584,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IBT_BDSLN</t>
+          <t>IBT_BDSLN7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IBT 1,2 BDSLN 500/150 kV</t>
+          <t>IBT 1,2 BDSLN7 500/150 kV</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>BDSLN</t>
+          <t>BDSLN7</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8623,17 +8623,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBT_BKASI</t>
+          <t>IBT_BKASI7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IBT 1,2,3,4 BKASI 500/150 kV</t>
+          <t>IBT 1,2,3,4 BKASI7 500/150 kV</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BKASI</t>
+          <t>BKASI7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -8662,17 +8662,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IBT_BLRJA</t>
+          <t>IBT_BLRJA7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>IBT 1,2,3,4 BLRJA 500/150 kV</t>
+          <t>IBT 1,2,3,4 BLRJA7 500/150 kV</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BLRJA</t>
+          <t>BLRJA7</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -8697,17 +8697,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IBT_BYOLI</t>
+          <t>IBT_BYOLI7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IBT 1,2 BYOLI 500/150 kV</t>
+          <t>IBT 1,2 BYOLI7 500/150 kV</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BYOLI</t>
+          <t>BYOLI7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IBT_CBATU</t>
+          <t>IBT_CBATU7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IBT 1,2,3,4 CBATU 500/150 kV</t>
+          <t>IBT 1,2,3,4 CBATU7 500/150 kV</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CBATU</t>
+          <t>CBATU7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -8775,17 +8775,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IBT_CIBNG</t>
+          <t>IBT_CIBNG7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IBT 1,2,3 CIBNG 500/150 kV</t>
+          <t>IBT 1,2,3 CIBNG7 500/150 kV</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CIBNG</t>
+          <t>CIBNG7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -8810,17 +8810,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IBT_CLGON</t>
+          <t>IBT_CLGON7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IBT 1,2,3,4 CLGON 500/150 kV</t>
+          <t>IBT 1,2,3,4 CLGON7 500/150 kV</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CLGON</t>
+          <t>CLGON7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -8849,17 +8849,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IBT_CRATA</t>
+          <t>IBT_CRATA7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IBT 1,2,3 CRATA 500/150 kV</t>
+          <t>IBT 1,2,3 CRATA7 500/150 kV</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CRATA</t>
+          <t>CRATA7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -8888,17 +8888,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IBT_CWANG</t>
+          <t>IBT_CWANG7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IBT 1,2,3 CWANG 500/150 kV</t>
+          <t>IBT 1,2,3 CWANG7 500/150 kV</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CWANG</t>
+          <t>CWANG7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -8927,17 +8927,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IBT_DEPOK</t>
+          <t>IBT_DEPOK7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IBT 1,2 DEPOK 500/150 kV</t>
+          <t>IBT 1,2 DEPOK7 500/150 kV</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DEPOK</t>
+          <t>DEPOK7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -8962,17 +8962,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IBT_DKSBI</t>
+          <t>IBT_DKSBI7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IBT 1,2 DKSBI 500/150 kV</t>
+          <t>IBT 1,2 DKSBI7 500/150 kV</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DKSBI</t>
+          <t>DKSBI7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -8997,17 +8997,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IBT_DLTMS</t>
+          <t>IBT_DLTMS7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IBT 1,2,3,4 DLTMS 500/150 kV</t>
+          <t>IBT 1,2,3,4 DLTMS7 500/150 kV</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DLTMS</t>
+          <t>DLTMS7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -9036,17 +9036,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IBT_GNDUL</t>
+          <t>IBT_GNDUL7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IBT 1,2,3,4 GNDUL 500/150 kV</t>
+          <t>IBT 1,2,3,4 GNDUL7 500/150 kV</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>GNDUL</t>
+          <t>GNDUL7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -9071,17 +9071,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IBT_GRATI</t>
+          <t>IBT_GRATI7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IBT 1,2,3 GRATI 500/150 kV</t>
+          <t>IBT 1,2,3 GRATI7 500/150 kV</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>GRATI</t>
+          <t>GRATI7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -9110,17 +9110,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IBT_GRSIK</t>
+          <t>IBT_GRSIK7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IBT 1,2 GRSIK 500/150 kV</t>
+          <t>IBT 1,2 GRSIK7 500/150 kV</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>GRSIK</t>
+          <t>GRSIK7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -9149,17 +9149,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IBT_KDIRI</t>
+          <t>IBT_KDIRI7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IBT 1,2,3,4 KDIRI 500/150 kV</t>
+          <t>IBT 1,2,3,4 KDIRI7 500/150 kV</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>KDIRI</t>
+          <t>KDIRI7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -9188,17 +9188,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IBT_KMBNG</t>
+          <t>IBT_KMBNG7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IBT 1,2 KMBNG 500/150 kV</t>
+          <t>IBT 1,2 KMBNG7 500/150 kV</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>KMBNG</t>
+          <t>KMBNG7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -9227,17 +9227,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IBT_KRIAN</t>
+          <t>IBT_KRIAN7</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IBT 1,2,3,4,5,6 KRIAN 500/150 kV</t>
+          <t>IBT 1,2,3,4,5,6 KRIAN7 500/150 kV</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>KRIAN</t>
+          <t>KRIAN7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9266,17 +9266,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IBT_KSGHN</t>
+          <t>IBT_KSGHN7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>IBT 1,2 KSGHN 500/150 kV</t>
+          <t>IBT 1,2 KSGHN7 500/150 kV</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>KSGHN</t>
+          <t>KSGHN7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IBT_LNGKG</t>
+          <t>IBT_LNGKG7</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IBT 1,2 LNGKG 500/150 kV</t>
+          <t>IBT 1,2 LNGKG7 500/150 kV</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LNGKG</t>
+          <t>LNGKG7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IBT_MDCAN</t>
+          <t>IBT_MDCAN7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IBT 1,2 MDCAN 500/150 kV</t>
+          <t>IBT 1,2 MDCAN7 500/150 kV</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MDCAN</t>
+          <t>MDCAN7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9379,17 +9379,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IBT_MKRNG</t>
+          <t>IBT_MKRNG7</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IBT 1,2 MKRNG 500/150 kV</t>
+          <t>IBT 1,2 MKRNG7 500/150 kV</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MKRNG</t>
+          <t>MKRNG7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9414,17 +9414,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IBT_MTWAR</t>
+          <t>IBT_MTWAR7</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>IBT 1,2 MTWAR 500/150 kV</t>
+          <t>IBT 1,2 MTWAR7 500/150 kV</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MTWAR</t>
+          <t>MTWAR7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -9449,17 +9449,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IBT_NBANG</t>
+          <t>IBT_NBANG7</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IBT 1,2 NBANG 500/150 kV</t>
+          <t>IBT 1,2 NBANG7 500/150 kV</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NBANG</t>
+          <t>NBANG7</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -9488,17 +9488,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IBT_PEDAN</t>
+          <t>IBT_PEDAN7</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IBT 1,2,3,4 PEDAN 500/150 kV</t>
+          <t>IBT 1,2,3,4 PEDAN7 500/150 kV</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PEDAN</t>
+          <t>PEDAN7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -9527,17 +9527,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IBT_PITON</t>
+          <t>IBT_PITON7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IBT 1,2,3 PITON 500/150 kV</t>
+          <t>IBT 1,2,3 PITON7 500/150 kV</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PITON</t>
+          <t>PITON7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -9566,17 +9566,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IBT_PMLNG</t>
+          <t>IBT_PMLNG7</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IBT 1,2 PMLNG 500/150 kV</t>
+          <t>IBT 1,2 PMLNG7 500/150 kV</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>PMLNG</t>
+          <t>PMLNG7</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -9605,17 +9605,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IBT_SKTNI</t>
+          <t>IBT_SKTNI7</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IBT 1,2 SKTNI 500/150 kV</t>
+          <t>IBT 1,2 SKTNI7 500/150 kV</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SKTNI</t>
+          <t>SKTNI7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -9640,17 +9640,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IBT_SRLYA</t>
+          <t>IBT_SRLYA7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IBT 1,2 SRLYA 500/150 kV</t>
+          <t>IBT 1,2 SRLYA7 500/150 kV</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SRLYA</t>
+          <t>SRLYA7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -9679,17 +9679,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IBT_TJATI</t>
+          <t>IBT_TJATI7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IBT 1,2 TJATI 500/150 kV</t>
+          <t>IBT 1,2 TJATI7 500/150 kV</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>TJATI</t>
+          <t>TJATI7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -9718,17 +9718,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IBT_TMBUN</t>
+          <t>IBT_TMBUN7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IBT 1,2 TMBUN 500/150 kV</t>
+          <t>IBT 1,2 TMBUN7 500/150 kV</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>TMBUN</t>
+          <t>TMBUN7</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -9757,17 +9757,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IBT_TSMYA</t>
+          <t>IBT_TSMYA7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IBT 1,2 TSMYA 500/150 kV</t>
+          <t>IBT 1,2 TSMYA7 500/150 kV</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>TSMYA</t>
+          <t>TSMYA7</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -9796,17 +9796,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IBT_UBRNG</t>
+          <t>IBT_UBRNG7</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IBT 1,2 UBRNG 500/150 kV</t>
+          <t>IBT 1,2 UBRNG7 500/150 kV</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>UBRNG</t>
+          <t>UBRNG7</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -9835,17 +9835,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IBT_UNGRN</t>
+          <t>IBT_UNGRN7</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IBT 1,2,3 UNGRN 500/150 kV</t>
+          <t>IBT 1,2,3 UNGRN7 500/150 kV</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>UNGRN</t>
+          <t>UNGRN7</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">

--- a/samples/system_ibt_500_ingest.xlsx
+++ b/samples/system_ibt_500_ingest.xlsx
@@ -8528,7 +8528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8554,25 +8554,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Jenis</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Tegangan</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
         </is>
@@ -8599,23 +8604,28 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
+      <c r="G2" t="n">
+        <v>1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -8638,23 +8648,28 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8677,19 +8692,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -8712,23 +8732,28 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
+      <c r="G5" t="n">
+        <v>1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>28;29</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -8751,23 +8776,28 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
+      <c r="G6" t="n">
+        <v>1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>10;11</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -8790,19 +8820,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -8825,23 +8860,28 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
+      <c r="G8" t="n">
+        <v>1</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -8864,23 +8904,28 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
+      <c r="G9" t="n">
+        <v>1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -8903,23 +8948,28 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
+      <c r="G10" t="n">
+        <v>1</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -8942,19 +8992,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8977,19 +9032,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -9012,23 +9072,28 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
+      <c r="G13" t="n">
+        <v>1</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -9051,19 +9116,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -9086,23 +9156,28 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
+      <c r="G15" t="n">
+        <v>1</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -9125,23 +9200,28 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
+      <c r="G16" t="n">
+        <v>1</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>30;31</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -9164,23 +9244,28 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
+      <c r="G17" t="n">
+        <v>1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>34;35</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -9203,23 +9288,28 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
+      <c r="G18" t="n">
+        <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -9242,23 +9332,28 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
+      <c r="G19" t="n">
+        <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -9281,23 +9376,28 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
+      <c r="G20" t="n">
+        <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -9320,19 +9420,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -9355,23 +9460,28 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
+      <c r="G22" t="n">
+        <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>7;8</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -9394,19 +9504,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -9429,19 +9544,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -9464,23 +9584,28 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
+      <c r="G25" t="n">
+        <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -9503,23 +9628,28 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
+      <c r="G26" t="n">
+        <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
           <t>23;24;25</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -9542,23 +9672,28 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
+      <c r="G27" t="n">
+        <v>1</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
           <t>37;38</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -9581,23 +9716,28 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
+      <c r="G28" t="n">
+        <v>1</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -9620,19 +9760,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -9655,23 +9800,28 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
+      <c r="G30" t="n">
+        <v>1</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
           <t>1;2</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -9694,23 +9844,28 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
+      <c r="G31" t="n">
+        <v>1</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
           <t>17;18;19;20</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -9733,23 +9888,28 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
+      <c r="G32" t="n">
+        <v>1</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -9772,23 +9932,28 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
+      <c r="G33" t="n">
+        <v>1</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -9811,23 +9976,28 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
+      <c r="G34" t="n">
+        <v>1</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -9850,23 +10020,28 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>IBT</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
+      <c r="G35" t="n">
+        <v>1</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
           <t>21;22</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
